--- a/data/output/2025/evaluasi_51.xlsx
+++ b/data/output/2025/evaluasi_51.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.2235258420521</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>50.24188651503058</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.19864517202218</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.141699226926913</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -694,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1146,118 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.22584875407184</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.322061201511382</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7.445809570016887</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,6 +1332,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Jembrana</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.82359506373698</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Jembrana</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Jembrana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.545439415404771</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5101</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Jembrana</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.61181461760714</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,6 +1630,146 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.80555918310939</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4689146589691877</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.369472349397428</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.014433346789004</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1340,6 +1844,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Badung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.689965996318408</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Badung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Badung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.487738550970009</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Badung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.237547645120553</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,6 +2030,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5105</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Klungkung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.12654084319839</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5105</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Klungkung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5105</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Klungkung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.828363908272605</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5105</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Klungkung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.552871754044817</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5105</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Klungkung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.299327101153817</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1428,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1488,6 +2244,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.512381013692357</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6785531822275191</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4319164398894956</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.497479787331807</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1502,7 +2398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,6 +2458,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5107</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Karangasem</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5107</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Karangasem</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9604694694071473</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1576,7 +2528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1650,18 +2602,270 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-1.838374281869538</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20.11919563600005</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05107459119806899</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.97856494527633</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4131846994483933</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.241058929242084</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.663496970323879</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.531440110076015</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>-2.573113765208192</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
